--- a/resultados/forecast_resultados.xlsx
+++ b/resultados/forecast_resultados.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -451,15 +451,15 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>72934.41734032059</v>
+        <v>72469.25565283633</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>72934.41734032084</v>
+        <v>65044.96526208999</v>
       </c>
     </row>
     <row r="4">
@@ -479,30 +479,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LinearPSOModel</t>
+          <t>LassoPSOModel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>65027.53786203758</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>706101</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RidgePSOModel</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="n">
-        <v>65027.13497764798</v>
+        <v>72466.51784057371</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +577,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -601,45 +585,45 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8613420.754276905</v>
+        <v>155872.1281960853</v>
       </c>
       <c r="D2" t="n">
-        <v>8669202.848706024</v>
+        <v>157152.146838692</v>
       </c>
       <c r="E2" t="n">
-        <v>8675036.060409503</v>
+        <v>158432.1654812986</v>
       </c>
       <c r="F2" t="n">
-        <v>8833097.857139641</v>
+        <v>159712.1841239053</v>
       </c>
       <c r="G2" t="n">
-        <v>8875504.69987822</v>
+        <v>160992.2027665119</v>
       </c>
       <c r="H2" t="n">
-        <v>9010525.90184547</v>
+        <v>162272.2214091185</v>
       </c>
       <c r="I2" t="n">
-        <v>9021803.28423257</v>
+        <v>163552.2400517251</v>
       </c>
       <c r="J2" t="n">
-        <v>9104979.443571031</v>
+        <v>164832.2586943318</v>
       </c>
       <c r="K2" t="n">
-        <v>9108158.919503564</v>
+        <v>166112.2773369384</v>
       </c>
       <c r="L2" t="n">
-        <v>9139969.133808376</v>
+        <v>167392.295979545</v>
       </c>
       <c r="M2" t="n">
-        <v>9245579.990679808</v>
+        <v>168672.3146221517</v>
       </c>
       <c r="N2" t="n">
-        <v>9308259.706067268</v>
+        <v>169952.3332647583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -647,40 +631,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8613420.754276901</v>
+        <v>143564.3649555349</v>
       </c>
       <c r="D3" t="n">
-        <v>8669202.848706024</v>
+        <v>135318.0511233675</v>
       </c>
       <c r="E3" t="n">
-        <v>8675036.060409505</v>
+        <v>160724.919626474</v>
       </c>
       <c r="F3" t="n">
-        <v>8833097.85713964</v>
+        <v>176611.6834663319</v>
       </c>
       <c r="G3" t="n">
-        <v>8875504.69987822</v>
+        <v>157922.3382455767</v>
       </c>
       <c r="H3" t="n">
-        <v>9010525.901845468</v>
+        <v>154193.4444307333</v>
       </c>
       <c r="I3" t="n">
-        <v>9021803.284232568</v>
+        <v>142162.6288882631</v>
       </c>
       <c r="J3" t="n">
-        <v>9104979.443571029</v>
+        <v>154680.6599669917</v>
       </c>
       <c r="K3" t="n">
-        <v>9108158.919503564</v>
+        <v>164953.3378656186</v>
       </c>
       <c r="L3" t="n">
-        <v>9139969.133808376</v>
+        <v>154052.5301048151</v>
       </c>
       <c r="M3" t="n">
-        <v>9245579.990679806</v>
+        <v>152713.002193048</v>
       </c>
       <c r="N3" t="n">
-        <v>9308259.706067268</v>
+        <v>153718.4513255323</v>
       </c>
     </row>
     <row r="4">
@@ -689,90 +673,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LinearPSOModel</t>
+          <t>LassoPSOModel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>158113.3183638413</v>
+        <v>155868.357014617</v>
       </c>
       <c r="D4" t="n">
-        <v>133317.4736634957</v>
+        <v>157148.3058205298</v>
       </c>
       <c r="E4" t="n">
-        <v>157960.9195557047</v>
+        <v>158428.2546264426</v>
       </c>
       <c r="F4" t="n">
-        <v>184696.6225319615</v>
+        <v>159708.2034323554</v>
       </c>
       <c r="G4" t="n">
-        <v>164788.616079192</v>
+        <v>160988.1522382682</v>
       </c>
       <c r="H4" t="n">
-        <v>144801.6601927998</v>
+        <v>162268.1010441809</v>
       </c>
       <c r="I4" t="n">
-        <v>134769.3509699093</v>
+        <v>163548.0498500937</v>
       </c>
       <c r="J4" t="n">
-        <v>147773.349955397</v>
+        <v>164827.9986560065</v>
       </c>
       <c r="K4" t="n">
-        <v>165033.7007932754</v>
+        <v>166107.9474619193</v>
       </c>
       <c r="L4" t="n">
-        <v>146679.9827456571</v>
+        <v>167387.896267832</v>
       </c>
       <c r="M4" t="n">
-        <v>128915.9765900306</v>
+        <v>168667.8450737448</v>
       </c>
       <c r="N4" t="n">
-        <v>156940.8012996833</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>706101</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RidgePSOModel</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>158112.7767294893</v>
-      </c>
-      <c r="D5" t="n">
-        <v>133316.4937580636</v>
-      </c>
-      <c r="E5" t="n">
-        <v>157960.0651329187</v>
-      </c>
-      <c r="F5" t="n">
-        <v>184696.0959026723</v>
-      </c>
-      <c r="G5" t="n">
-        <v>164788.3006005601</v>
-      </c>
-      <c r="H5" t="n">
-        <v>144801.1688572089</v>
-      </c>
-      <c r="I5" t="n">
-        <v>134768.3155203213</v>
-      </c>
-      <c r="J5" t="n">
-        <v>147772.2965534924</v>
-      </c>
-      <c r="K5" t="n">
-        <v>165032.6974684559</v>
-      </c>
-      <c r="L5" t="n">
-        <v>146678.9498593124</v>
-      </c>
-      <c r="M5" t="n">
-        <v>128914.7486271921</v>
-      </c>
-      <c r="N5" t="n">
-        <v>156939.7118152867</v>
+        <v>169947.7938796576</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,7 +806,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -876,48 +814,48 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8851805.83875096</v>
+        <v>147231.684780846</v>
       </c>
       <c r="D2" t="n">
-        <v>8928058.325976254</v>
+        <v>149324.240666847</v>
       </c>
       <c r="E2" t="n">
-        <v>9004829.00808798</v>
+        <v>151416.7965528481</v>
       </c>
       <c r="F2" t="n">
-        <v>9081651.778607132</v>
+        <v>153509.3524388492</v>
       </c>
       <c r="G2" t="n">
-        <v>9158686.893809324</v>
+        <v>155601.9083248502</v>
       </c>
       <c r="H2" t="n">
-        <v>9236336.180886487</v>
+        <v>157694.4642108513</v>
       </c>
       <c r="I2" t="n">
-        <v>9314343.425422685</v>
+        <v>159787.0200968524</v>
       </c>
       <c r="J2" t="n">
-        <v>9392404.992680127</v>
+        <v>161879.5759828534</v>
       </c>
       <c r="K2" t="n">
-        <v>9470452.131794555</v>
+        <v>163972.1318688544</v>
       </c>
       <c r="L2" t="n">
-        <v>9548485.944076149</v>
+        <v>166064.6877548555</v>
       </c>
       <c r="M2" t="n">
-        <v>9626509.661062779</v>
+        <v>168157.2436408566</v>
       </c>
       <c r="N2" t="n">
-        <v>9704523.884137625</v>
+        <v>170249.7995268576</v>
       </c>
       <c r="O2" t="n">
-        <v>9782530.064892719</v>
+        <v>172342.3554128587</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -925,43 +863,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8851805.83875096</v>
+        <v>123909.8142642996</v>
       </c>
       <c r="D3" t="n">
-        <v>8928058.325976247</v>
+        <v>142981.6150873551</v>
       </c>
       <c r="E3" t="n">
-        <v>9004829.008087976</v>
+        <v>149287.0124653175</v>
       </c>
       <c r="F3" t="n">
-        <v>9081651.778607128</v>
+        <v>152421.8311365219</v>
       </c>
       <c r="G3" t="n">
-        <v>9158686.89380932</v>
+        <v>154769.2260529481</v>
       </c>
       <c r="H3" t="n">
-        <v>9236336.180886479</v>
+        <v>156921.0616639809</v>
       </c>
       <c r="I3" t="n">
-        <v>9314343.425422678</v>
+        <v>159024.3294718531</v>
       </c>
       <c r="J3" t="n">
-        <v>9392404.992680123</v>
+        <v>161115.5353044637</v>
       </c>
       <c r="K3" t="n">
-        <v>9470452.131794551</v>
+        <v>163203.7455054471</v>
       </c>
       <c r="L3" t="n">
-        <v>9548485.944076145</v>
+        <v>165291.211731364</v>
       </c>
       <c r="M3" t="n">
-        <v>9626509.661062775</v>
+        <v>167378.4931886018</v>
       </c>
       <c r="N3" t="n">
-        <v>9704523.884137625</v>
+        <v>169465.7287579242</v>
       </c>
       <c r="O3" t="n">
-        <v>9782530.064892715</v>
+        <v>171552.9529308303</v>
       </c>
     </row>
     <row r="4">
@@ -970,47 +908,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LinearPSOModel</t>
+          <t>LassoPSOModel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>161495.0784480509</v>
+        <v>147228.2971093575</v>
       </c>
       <c r="D4" t="n">
-        <v>162594.8867048162</v>
+        <v>149320.796534167</v>
       </c>
       <c r="E4" t="n">
-        <v>169064.1657144296</v>
+        <v>151413.2959589766</v>
       </c>
       <c r="F4" t="n">
-        <v>151486.2429843115</v>
+        <v>153505.7953837862</v>
       </c>
       <c r="G4" t="n">
-        <v>161334.9997177599</v>
+        <v>155598.2948085958</v>
       </c>
       <c r="H4" t="n">
-        <v>172204.0015897233</v>
+        <v>157690.7942334054</v>
       </c>
       <c r="I4" t="n">
-        <v>166257.3069162483</v>
+        <v>159783.293658215</v>
       </c>
       <c r="J4" t="n">
-        <v>164497.2376274854</v>
+        <v>161875.7930830246</v>
       </c>
       <c r="K4" t="n">
-        <v>164610.0222326928</v>
+        <v>163968.2925078342</v>
       </c>
       <c r="L4" t="n">
-        <v>161070.7200957547</v>
+        <v>166060.7919326438</v>
       </c>
       <c r="M4" t="n">
-        <v>183094.7380003012</v>
+        <v>168153.2913574534</v>
       </c>
       <c r="N4" t="n">
-        <v>188695.8673279789</v>
+        <v>170245.7907822629</v>
       </c>
       <c r="O4" t="n">
-        <v>194208.5698369881</v>
+        <v>172338.2902070725</v>
       </c>
     </row>
     <row r="5">
@@ -1019,96 +957,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RidgePSOModel</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>161494.0675263302</v>
+        <v>135570.7495225728</v>
       </c>
       <c r="D5" t="n">
-        <v>162593.608845358</v>
+        <v>146152.927877101</v>
       </c>
       <c r="E5" t="n">
-        <v>169062.8468170177</v>
+        <v>150351.9045090828</v>
       </c>
       <c r="F5" t="n">
-        <v>151485.0516140737</v>
+        <v>152965.5917876856</v>
       </c>
       <c r="G5" t="n">
-        <v>161333.9483510643</v>
+        <v>155185.5671888992</v>
       </c>
       <c r="H5" t="n">
-        <v>172203.08894294</v>
+        <v>157307.762937416</v>
       </c>
       <c r="I5" t="n">
-        <v>166256.2342694097</v>
+        <v>159405.6747843527</v>
       </c>
       <c r="J5" t="n">
-        <v>164496.1048629241</v>
+        <v>161497.5556436585</v>
       </c>
       <c r="K5" t="n">
-        <v>164608.8370680944</v>
+        <v>163587.9386871507</v>
       </c>
       <c r="L5" t="n">
-        <v>161069.4070112814</v>
+        <v>165677.9497431098</v>
       </c>
       <c r="M5" t="n">
-        <v>183093.4557423308</v>
+        <v>167767.8684147292</v>
       </c>
       <c r="N5" t="n">
-        <v>188694.5547747305</v>
+        <v>169857.764142391</v>
       </c>
       <c r="O5" t="n">
-        <v>194207.2945501998</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>706101</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ensemble</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>161494.5729871905</v>
-      </c>
-      <c r="D6" t="n">
-        <v>162594.2477750871</v>
-      </c>
-      <c r="E6" t="n">
-        <v>169063.5062657236</v>
-      </c>
-      <c r="F6" t="n">
-        <v>151485.6472991926</v>
-      </c>
-      <c r="G6" t="n">
-        <v>161334.4740344121</v>
-      </c>
-      <c r="H6" t="n">
-        <v>172203.5452663317</v>
-      </c>
-      <c r="I6" t="n">
-        <v>166256.770592829</v>
-      </c>
-      <c r="J6" t="n">
-        <v>164496.6712452048</v>
-      </c>
-      <c r="K6" t="n">
-        <v>164609.4296503936</v>
-      </c>
-      <c r="L6" t="n">
-        <v>161070.0635535181</v>
-      </c>
-      <c r="M6" t="n">
-        <v>183094.096871316</v>
-      </c>
-      <c r="N6" t="n">
-        <v>188695.2110513547</v>
-      </c>
-      <c r="O6" t="n">
-        <v>194207.932193594</v>
+        <v>171947.6541718445</v>
       </c>
     </row>
   </sheetData>
@@ -1122,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,34 +1038,18 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109102</v>
+        <v>706101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LinearPSOModel</t>
+          <t>RidgePSOModel</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>72934.41734032059</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>706101</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RidgePSOModel</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" t="n">
-        <v>65027.13497764798</v>
+        <v>65044.96526208999</v>
       </c>
     </row>
   </sheetData>
